--- a/public/samples/bb-templates/BB-Template-Import-ccp-vii-lev.xlsx
+++ b/public/samples/bb-templates/BB-Template-Import-ccp-vii-lev.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -444,6 +444,9 @@
       <c r="M1" t="str">
         <v>detect_keys</v>
       </c>
+      <c r="N1" t="str">
+        <v>auto_discover_tabs</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -453,10 +456,10 @@
         <v>Silicon Valley Bank</v>
       </c>
       <c r="C2" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="D2" t="str">
-        <v>Investor List</v>
+        <v/>
       </c>
       <c r="E2">
         <v>7</v>
@@ -468,10 +471,10 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -485,10 +488,13 @@
       <c r="M2" t="str">
         <v/>
       </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -528,7 +534,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>Investor List</v>
+        <v/>
       </c>
       <c r="D2">
         <v>7</v>
@@ -552,95 +558,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>tab_role</v>
-      </c>
-      <c r="B1" t="str">
-        <v>group_sort</v>
-      </c>
-      <c r="C1" t="str">
-        <v>header_text</v>
-      </c>
-      <c r="D1" t="str">
-        <v>classification</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>LP_GRID</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Levered (Delaware) Feeder</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Included</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>LP_GRID</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="str">
-        <v>(Cayman) Feeder, L.P.</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Included</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>LP_GRID</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="str">
-        <v>(Delaware) Feeder, L.P.</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Included</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>LP_GRID</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Lux Intermediate</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Included</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>LP_GRID</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Lux Non-Treaty Feeder</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Included</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1:A2"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -782,7 +703,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Group headers are feeder vehicles (not credit-tier categories); each followed by a total.</v>
+        <v>Each visible feeder tab is a Fund Sleeve. Do not map feeder names as LP Category groups.</v>
       </c>
     </row>
   </sheetData>
